--- a/site/data/downloads/france.xlsx
+++ b/site/data/downloads/france.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="물가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="고용" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="성장" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="유가" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="금리" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유가" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금리" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/france.xlsx
+++ b/site/data/downloads/france.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1852,6 +1852,16 @@
       </c>
       <c r="B60" t="n">
         <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2724,6 +2734,16 @@
       </c>
       <c r="B61" t="n">
         <v>91.08</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>114.08</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/france.xlsx
+++ b/site/data/downloads/france.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1226,6 +1226,19 @@
       </c>
       <c r="C61" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/france.xlsx
+++ b/site/data/downloads/france.xlsx
@@ -2770,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3395,6 +3395,16 @@
         <v>4</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/france.xlsx
+++ b/site/data/downloads/france.xlsx
@@ -1252,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1875,6 +1875,16 @@
       </c>
       <c r="B61" t="n">
         <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2111,6 +2121,16 @@
       </c>
       <c r="B21" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
